--- a/data/detallesBasedatosNatural.xlsx
+++ b/data/detallesBasedatosNatural.xlsx
@@ -53,7 +53,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -66,6 +66,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -464,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="11.42578125" customWidth="1" style="1" min="1" max="1"/>
@@ -1670,156 +1673,220 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>12345</t>
-        </is>
+      <c r="A32" t="n">
+        <v>3</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>465489</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>MAXIMILIUS ALFA MOSQUERA RUIZ</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>147487554001</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>147487554</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>PLANILLA DE APORTES</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>142,69</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>258,63</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>336,00</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Dr. Jorge Gonzalo Atiencia Gálvez</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Dr. Heredia Guano Jorge Mateo</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>1472787</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
           <t>Pedro Alfonso Pedro Porro</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>1414141441001</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>1414141441</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>PLANILLA DE APORTES</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>142,58</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>185,25</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>240,00</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>1,258,00</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>1,744,00</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>2267,00</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>Dr. Jorge Gonzalo Atiencia Gálvez</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K33" s="5" t="inlineStr">
         <is>
           <t>Ing. Alfonso Reinoso Luis Eduardo</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>234567</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>123135</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Pedro Alfonso Pedro Porro</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>1414141441001</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>1414141441</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>PLANILLA DE APORTES</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>147,36</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>258,36</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>335,00</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>12,00</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>12,00</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>15,00</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>Dr. Jorge Gonzalo Atiencia Gálvez</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K34" s="5" t="inlineStr">
         <is>
           <t>Ing. Alfonso Reinoso Luis Eduardo</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>58692</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>Pedro Alfonso Pedro Porro</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>1414141441001</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>1414141441</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>PLANILLA DE APORTES</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>196,38</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>278,45</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>361,00</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>132,00</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>3,123,00</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>4059,00</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>Dr. Jorge Gonzalo Atiencia Gálvez</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K35" s="5" t="inlineStr">
         <is>
           <t>Ing. Alfonso Reinoso Luis Eduardo</t>
         </is>
